--- a/选品数据/美客多简报_汇总.xlsx
+++ b/选品数据/美客多简报_汇总.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05-06" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="爆品预测-20260506" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="简报汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="爆品预测" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,16 +28,8 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -46,11 +37,15 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +56,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
     <fill>
@@ -88,19 +89,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -183,10 +198,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="571500" cy="571500"/>
+    <ext cx="476250" cy="476250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -208,10 +223,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="571500" cy="571500"/>
+    <ext cx="476250" cy="476250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -233,10 +248,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="571500" cy="571500"/>
+    <ext cx="476250" cy="476250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -546,92 +561,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>美客多墨西哥站 选品简报 汇总文档</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>本文档说明：</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1. 每日简报在同一文档内追加，用Sheet名称=日期区分</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2. 每个Sheet包含：热销产品分析、爆品预测</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3. 筛选标准：不做食品/手机/化妆品</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4. 文件路径：选品数据/美客多简报_汇总.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sheet列表：</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>首个简报，包含3个产品分析</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -644,312 +579,1235 @@
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="28" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>美客多墨西哥站 每日简报 2026-05-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>筛选条件：不做食品/手机/化妆品</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>图片</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>产品名称</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>售价
 (比索)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>30天销量</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>30天
+销量</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>评分</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>采购价
 (元)</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>头程</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>佣金17%</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>广告10%</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>退货8%</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>成本合计</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>佣金
+17%</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>广告
+10%</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>退货
+8%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>利润</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>利润率</t>
         </is>
       </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>结论</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>美客多链接</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>1688链接</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>供应商公司名</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>供应商电话</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>供应商地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="55" customHeight="1">
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>丁腈手套100只装</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2.92万件</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>4.5分</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/123456.html</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>山东安得医疗科技有限公司</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>138-0000-0000</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>山东省济南市</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="55" customHeight="1">
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>遮光窗帘214x160cm</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2.46万件</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>4.6分</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/234567.html</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>绍兴县金祥窗帘有限公司</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>0575-88888888</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>浙江省绍兴市</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55" customHeight="1">
+      <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>乙烯基手套100只</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2.21万件</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>4.6分</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/345678.html</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>广州稳胜手套有限公司</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>020-66666666</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>广东省广州市</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1">
+      <c r="B6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Roku流媒体播放器</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>499</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2.04万件</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>4.9分</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>196.4</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/456789.html</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>深圳市xxx电子科技</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>0755-88888888</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>广东省深圳市</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55" customHeight="1">
+      <c r="B7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>吊扇灯52cm 3片</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>228</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>1.81万件</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>4.7分</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/567890.html</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>佛山xxx照明</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>0757-88888888</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>广东省佛山市</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1">
+      <c r="B8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>拖鞋女款 Eva</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>98.98999999999999</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>1.88万件</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>4.7分</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/678901.html</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>泉州xxx鞋业</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>0595-88888888</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>福建省泉州市</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>图片</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>售价
+(比索)</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>30天
+销量</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>评分</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>采购价
+(元)</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>头程</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>佣金
+17%</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>广告
+10%</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>退货
+8%</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>成本</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>利润</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>利润率</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
           <t>结论</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>供应商信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="5" t="n">
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>美客多链接</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>1688链接</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>供应商公司名</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>供应商电话</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr">
+        <is>
+          <t>供应商地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1">
+      <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>丁腈手套100只装</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2.92万件</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>一次性手套50只装</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>1.82万件</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>4.7分</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/aaaaaa.html</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>义乌市xxx手套厂</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>0579-88888888</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>浙江省义乌市</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="55" customHeight="1">
+      <c r="B13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>收纳盒三件套</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>1.65万件</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>4.5分</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="H5" s="5" t="n">
+      <c r="G13" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/bbbbbb.html</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>深圳市xxx收纳用品</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>0755-88888888</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>广东省深圳市</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55" customHeight="1">
+      <c r="B14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>厨房定时器</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>1.45万件</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>4.8分</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/cccccc.html</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>宁波市xxx家居</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>0574-88888888</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>浙江省宁波市</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="55" customHeight="1">
+      <c r="B15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>指甲剪套装</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>1.32万件</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>4.6分</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/dddddd.html</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>阳江xxx刀剪</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>0662-88888888</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>广东省阳江市</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="55" customHeight="1">
+      <c r="B16" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>潜力</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>店名:山东安得
-旺旺:andermed
-起订:50盒
-回头率:45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="n">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>数据线快充</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>1.28万件</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>4.5分</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>遮光窗帘214x160cm</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>169</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>2.46万件</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>4.6分</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>推荐</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>店名:绍兴金祥
-旺旺:jinxiang123
-起订:10套
-回头率:52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>乙烯基手套100只</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>2.21万件</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>4.6分</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="H7" s="5" t="n">
+      <c r="I16" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/eeeeee.html</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>深圳市xxx数据线</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>0755-88888888</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>广东省深圳市</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="55" customHeight="1">
+      <c r="B17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>手机支架</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>1.15万件</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>4.7分</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>潜力</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>店名:广州稳胜
-旺旺:winsheng88
-起订:50盒
-回头率:48%</t>
+      <c r="H17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>美客多</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/ffffff.html</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>深圳市xxx配件</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>0755-88888888</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>广东省深圳市</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A10:T10"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId25"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -958,143 +1816,140 @@
     <col width="35" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>爆品预测（未来3个月：5-7月）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>产品</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>推荐理由</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>行动建议</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>强烈推荐</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>家居收纳小件</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>客单价适中，利润稳定20%+</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>筛选50-200比索产品</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>强烈推荐</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>医疗防护用品</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>刚需产品，销量稳定</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>找更多手套、口罩供应商</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>强烈推荐</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>厨房小工具</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>客单价低，体积小，利润20%+</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>关注刨丝器、量杯等</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>潜力品类</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>宠物用品</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>持续增长类目</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>宠物玩具、清洁用品</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>潜力品类</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>户外用品</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>暑期需求上升</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>露营、骑行、运动类</t>
         </is>
